--- a/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{182B053A-8B91-4D26-A51A-420628FDE43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B3D8EB-C776-458E-B1EE-31D80BEE1CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -945,187 +945,187 @@
     <t>~fi_comm</t>
   </si>
   <si>
-    <t>e_w113757307-220_HRV</t>
+    <t>e_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>grid node -- way/43337263-400 (Split, 11 km)</t>
+  </si>
+  <si>
+    <t>lo</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV</t>
+  </si>
+  <si>
+    <t>grid node -- way/163860997-400 (Zadar, 43 km)</t>
+  </si>
+  <si>
+    <t>e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>grid node -- way/96704507-220 (Zagreb, 83 km)</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>grid node -- way/273326173-220 (Rijeka, 65 km)</t>
+  </si>
+  <si>
+    <t>e_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>grid node -- way/89823918-400 (Osijek, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV</t>
+  </si>
+  <si>
+    <t>grid node -- way/210745193-220 (Rijeka, 30 km)</t>
+  </si>
+  <si>
+    <t>e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>grid node -- way/89817617-400 (Rijeka, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>grid node -- way/89819945-220 (Zagreb, 19 km)</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>grid node -- way/162022271-220 (Split, 51 km)</t>
+  </si>
+  <si>
+    <t>e_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>grid node -- way/170366194-220 (Zagreb, 53 km)</t>
+  </si>
+  <si>
+    <t>e_Split_HRV</t>
+  </si>
+  <si>
+    <t>grid node -- way/43337263-220 (Split, 11 km)</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>grid node -- way/89818719-400 (Zagreb, 17 km)</t>
+  </si>
+  <si>
+    <t>e_Vinkovci_HRV</t>
   </si>
   <si>
     <t>grid node -- way/113757307-220 (Osijek, 36 km)</t>
   </si>
   <si>
-    <t>lo</t>
-  </si>
-  <si>
-    <t>e_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>grid node -- way/162022271-220 (Split, 51 km)</t>
-  </si>
-  <si>
-    <t>e_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>grid node -- way/163860997-400 (Zadar, 43 km)</t>
-  </si>
-  <si>
-    <t>e_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>grid node -- way/170366194-220 (Zagreb, 53 km)</t>
-  </si>
-  <si>
-    <t>e_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>grid node -- way/210745193-220 (Rijeka, 30 km)</t>
-  </si>
-  <si>
-    <t>e_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>grid node -- way/273326173-220 (Rijeka, 65 km)</t>
-  </si>
-  <si>
-    <t>e_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>grid node -- way/43337263-220 (Split, 11 km)</t>
-  </si>
-  <si>
-    <t>e_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>grid node -- way/43337263-400 (Split, 11 km)</t>
-  </si>
-  <si>
-    <t>e_w89817617-220_HRV</t>
+    <t>e_Viskovo_HRV</t>
   </si>
   <si>
     <t>grid node -- way/89817617-220 (Rijeka, 10 km)</t>
   </si>
   <si>
-    <t>e_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>grid node -- way/89817617-400 (Rijeka, 10 km)</t>
-  </si>
-  <si>
-    <t>e_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>grid node -- way/89818719-400 (Zagreb, 17 km)</t>
-  </si>
-  <si>
-    <t>e_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>grid node -- way/89819945-220 (Zagreb, 19 km)</t>
-  </si>
-  <si>
-    <t>e_w89820062-400_HRV</t>
+    <t>e_Zagreb_HRV</t>
   </si>
   <si>
     <t>grid node -- way/89820062-400 (Zagreb, 16 km)</t>
   </si>
   <si>
-    <t>e_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>grid node -- way/89823918-400 (Osijek, 10 km)</t>
-  </si>
-  <si>
-    <t>e_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>grid node -- way/96704507-220 (Zagreb, 83 km)</t>
-  </si>
-  <si>
-    <t>h_w113757307-220_HRV</t>
+    <t>h_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/43337263-400 (Split, 11 km)</t>
+  </si>
+  <si>
+    <t>h_Knin_HRV</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/163860997-400 (Zadar, 43 km)</t>
+  </si>
+  <si>
+    <t>h_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/96704507-220 (Zagreb, 83 km)</t>
+  </si>
+  <si>
+    <t>h_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/273326173-220 (Rijeka, 65 km)</t>
+  </si>
+  <si>
+    <t>h_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/89823918-400 (Osijek, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Pula_HRV</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/210745193-220 (Rijeka, 30 km)</t>
+  </si>
+  <si>
+    <t>h_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/89817617-400 (Rijeka, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/89819945-220 (Zagreb, 19 km)</t>
+  </si>
+  <si>
+    <t>h_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/162022271-220 (Split, 51 km)</t>
+  </si>
+  <si>
+    <t>h_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/170366194-220 (Zagreb, 53 km)</t>
+  </si>
+  <si>
+    <t>h_Split_HRV</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/43337263-220 (Split, 11 km)</t>
+  </si>
+  <si>
+    <t>h_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/89818719-400 (Zagreb, 17 km)</t>
+  </si>
+  <si>
+    <t>h_Vinkovci_HRV</t>
   </si>
   <si>
     <t>heat at grid node -- way/113757307-220 (Osijek, 36 km)</t>
   </si>
   <si>
-    <t>h_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/162022271-220 (Split, 51 km)</t>
-  </si>
-  <si>
-    <t>h_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/163860997-400 (Zadar, 43 km)</t>
-  </si>
-  <si>
-    <t>h_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/170366194-220 (Zagreb, 53 km)</t>
-  </si>
-  <si>
-    <t>h_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/210745193-220 (Rijeka, 30 km)</t>
-  </si>
-  <si>
-    <t>h_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/273326173-220 (Rijeka, 65 km)</t>
-  </si>
-  <si>
-    <t>h_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/43337263-220 (Split, 11 km)</t>
-  </si>
-  <si>
-    <t>h_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/43337263-400 (Split, 11 km)</t>
-  </si>
-  <si>
-    <t>h_w89817617-220_HRV</t>
+    <t>h_Viskovo_HRV</t>
   </si>
   <si>
     <t>heat at grid node -- way/89817617-220 (Rijeka, 10 km)</t>
   </si>
   <si>
-    <t>h_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/89817617-400 (Rijeka, 10 km)</t>
-  </si>
-  <si>
-    <t>h_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/89818719-400 (Zagreb, 17 km)</t>
-  </si>
-  <si>
-    <t>h_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/89819945-220 (Zagreb, 19 km)</t>
-  </si>
-  <si>
-    <t>h_w89820062-400_HRV</t>
+    <t>h_Zagreb_HRV</t>
   </si>
   <si>
     <t>heat at grid node -- way/89820062-400 (Zagreb, 16 km)</t>
-  </si>
-  <si>
-    <t>h_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/89823918-400 (Osijek, 10 km)</t>
-  </si>
-  <si>
-    <t>h_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/96704507-220 (Zagreb, 83 km)</t>
   </si>
 </sst>
 </file>
@@ -3540,7 +3540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC29C7D9-A9BB-4B66-A47A-94ADF01A1747}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6154591-CA8E-4EE9-8D27-58F61333ED7F}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8989F1E7-7CED-4F97-867D-7848A9822808}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F707B2E-4402-4D60-BD41-2E6F8DC72281}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B3D8EB-C776-458E-B1EE-31D80BEE1CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48026CDA-1453-4F29-8BF8-E943A3C9BE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3540,7 +3540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6154591-CA8E-4EE9-8D27-58F61333ED7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0CE4614-963F-45E3-8495-D265CE1A40A2}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F707B2E-4402-4D60-BD41-2E6F8DC72281}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B7723F2-5491-4661-AE8D-BAB19DBD7E4D}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48026CDA-1453-4F29-8BF8-E943A3C9BE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6C607E-30A3-48A2-8C95-A98EC8A51BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3540,7 +3540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0CE4614-963F-45E3-8495-D265CE1A40A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C45988-71EE-4830-AB26-C1E54024BF2C}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B7723F2-5491-4661-AE8D-BAB19DBD7E4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16CC1348-C030-4BBC-83F7-97A2764DCE03}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6C607E-30A3-48A2-8C95-A98EC8A51BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6686A17D-EAF9-41CE-A48D-BE7F319E146B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3540,7 +3540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C45988-71EE-4830-AB26-C1E54024BF2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E7EBF4-9717-4F19-9164-E4DEB61D7D9E}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16CC1348-C030-4BBC-83F7-97A2764DCE03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA15A937-5278-48F7-842C-970FDE22C566}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6686A17D-EAF9-41CE-A48D-BE7F319E146B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EBBF0C-BBEA-4EB1-9142-8651EC673C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3540,7 +3540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E7EBF4-9717-4F19-9164-E4DEB61D7D9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC797B3C-BD4F-465A-BC4F-8DCB0DD09869}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -3971,7 +3971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA15A937-5278-48F7-842C-970FDE22C566}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53B1848-4D56-4187-89FF-9B80356B6D6F}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EBBF0C-BBEA-4EB1-9142-8651EC673C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F3D4AD-90ED-4615-BCB1-90223D0F843E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
-    <sheet name="heat" sheetId="8" r:id="rId2"/>
-    <sheet name="grids" sheetId="7" r:id="rId3"/>
-    <sheet name="fuels" sheetId="2" r:id="rId4"/>
-    <sheet name="TimePeriods" sheetId="3" r:id="rId5"/>
-    <sheet name="System Settings" sheetId="4" r:id="rId6"/>
-    <sheet name="Constants" sheetId="5" r:id="rId7"/>
-    <sheet name="reporting options" sheetId="6" r:id="rId8"/>
+    <sheet name="co2_network" sheetId="9" r:id="rId2"/>
+    <sheet name="heat" sheetId="8" r:id="rId3"/>
+    <sheet name="grids" sheetId="7" r:id="rId4"/>
+    <sheet name="fuels" sheetId="2" r:id="rId5"/>
+    <sheet name="TimePeriods" sheetId="3" r:id="rId6"/>
+    <sheet name="System Settings" sheetId="4" r:id="rId7"/>
+    <sheet name="Constants" sheetId="5" r:id="rId8"/>
+    <sheet name="reporting options" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="446">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -864,6 +865,72 @@
     <t>solar electricity generation in cluster -- 15</t>
   </si>
   <si>
+    <t>elc_wof_HRV_001</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_002</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_003</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_004</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_006</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_007</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_008</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_009</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_010</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_011</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 11</t>
+  </si>
+  <si>
     <t>elc_won_HRV_001</t>
   </si>
   <si>
@@ -1126,6 +1193,192 @@
   </si>
   <si>
     <t>heat at grid node -- way/89820062-400 (Zagreb, 16 km)</t>
+  </si>
+  <si>
+    <t>co2_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/113757307-220 (Osijek, 36 km)</t>
+  </si>
+  <si>
+    <t>co2_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/162022271-220 (Split, 51 km)</t>
+  </si>
+  <si>
+    <t>co2_Knin_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/163860997-400 (Zadar, 43 km)</t>
+  </si>
+  <si>
+    <t>co2_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/170366194-220 (Zagreb, 53 km)</t>
+  </si>
+  <si>
+    <t>co2_Pula_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/210745193-220 (Rijeka, 30 km)</t>
+  </si>
+  <si>
+    <t>co2_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/273326173-220 (Rijeka, 65 km)</t>
+  </si>
+  <si>
+    <t>co2_Split_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/43337263-220 (Split, 11 km)</t>
+  </si>
+  <si>
+    <t>co2_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/43337263-400 (Split, 11 km)</t>
+  </si>
+  <si>
+    <t>co2_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/89817617-220 (Rijeka, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/89817617-400 (Rijeka, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/89818719-400 (Zagreb, 17 km)</t>
+  </si>
+  <si>
+    <t>co2_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/89819945-220 (Zagreb, 19 km)</t>
+  </si>
+  <si>
+    <t>co2_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/89820062-400 (Zagreb, 16 km)</t>
+  </si>
+  <si>
+    <t>co2_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/89823918-400 (Osijek, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/96704507-220 (Zagreb, 83 km)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10893_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10893.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10894_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10894.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10895_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10895.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10896_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10896.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10897_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10897.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10898_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10898.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10899_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10899.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10900_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10900.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10901_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10901.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10902_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10902.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10903_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10903.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10904_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10904.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10906_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10906.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci10907_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_10907.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11249_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11249.0 (OGCI/catalogue)</t>
+  </si>
+  <si>
+    <t>co2s_ogci11250_HRV</t>
+  </si>
+  <si>
+    <t>co2 delivered to sink -- ogci_11250.0 (OGCI/catalogue)</t>
   </si>
 </sst>
 </file>
@@ -3540,16 +3793,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC797B3C-BD4F-465A-BC4F-8DCB0DD09869}">
-  <dimension ref="B3:I19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE3CBE1-B133-430B-AC96-CB0323706611}">
+  <dimension ref="B3:H35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="3" spans="2:9">
+    <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
         <v>218</v>
       </c>
@@ -3563,406 +3816,726 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:8">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>332</v>
+        <v>384</v>
       </c>
       <c r="D5" t="s">
         <v>241</v>
       </c>
       <c r="E5" t="s">
-        <v>333</v>
+        <v>385</v>
       </c>
       <c r="F5" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H5" t="s">
-        <v>303</v>
-      </c>
-      <c r="I5" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>334</v>
+        <v>386</v>
       </c>
       <c r="D6" t="s">
         <v>241</v>
       </c>
       <c r="E6" t="s">
-        <v>335</v>
+        <v>387</v>
       </c>
       <c r="F6" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H6" t="s">
-        <v>303</v>
-      </c>
-      <c r="I6" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
       <c r="B7" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>336</v>
+        <v>388</v>
       </c>
       <c r="D7" t="s">
         <v>241</v>
       </c>
       <c r="E7" t="s">
-        <v>337</v>
+        <v>389</v>
       </c>
       <c r="F7" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H7" t="s">
-        <v>303</v>
-      </c>
-      <c r="I7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
       <c r="B8" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>338</v>
+        <v>390</v>
       </c>
       <c r="D8" t="s">
         <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>339</v>
+        <v>391</v>
       </c>
       <c r="F8" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H8" t="s">
-        <v>303</v>
-      </c>
-      <c r="I8" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
       <c r="B9" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>340</v>
+        <v>392</v>
       </c>
       <c r="D9" t="s">
         <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="F9" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H9" t="s">
-        <v>303</v>
-      </c>
-      <c r="I9" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
       <c r="B10" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>342</v>
+        <v>394</v>
       </c>
       <c r="D10" t="s">
         <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>343</v>
+        <v>395</v>
       </c>
       <c r="F10" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H10" t="s">
-        <v>303</v>
-      </c>
-      <c r="I10" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
       <c r="B11" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>344</v>
+        <v>396</v>
       </c>
       <c r="D11" t="s">
         <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="F11" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H11" t="s">
-        <v>303</v>
-      </c>
-      <c r="I11" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
       <c r="B12" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>346</v>
+        <v>398</v>
       </c>
       <c r="D12" t="s">
         <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>347</v>
+        <v>399</v>
       </c>
       <c r="F12" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H12" t="s">
-        <v>303</v>
-      </c>
-      <c r="I12" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
       <c r="B13" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>348</v>
+        <v>400</v>
       </c>
       <c r="D13" t="s">
         <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>349</v>
+        <v>401</v>
       </c>
       <c r="F13" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H13" t="s">
-        <v>303</v>
-      </c>
-      <c r="I13" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
       <c r="B14" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>350</v>
+        <v>402</v>
       </c>
       <c r="D14" t="s">
         <v>241</v>
       </c>
       <c r="E14" t="s">
-        <v>351</v>
+        <v>403</v>
       </c>
       <c r="F14" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H14" t="s">
-        <v>303</v>
-      </c>
-      <c r="I14" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
       <c r="B15" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>352</v>
+        <v>404</v>
       </c>
       <c r="D15" t="s">
         <v>241</v>
       </c>
       <c r="E15" t="s">
-        <v>353</v>
+        <v>405</v>
       </c>
       <c r="F15" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H15" t="s">
-        <v>303</v>
-      </c>
-      <c r="I15" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
       <c r="B16" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>354</v>
+        <v>406</v>
       </c>
       <c r="D16" t="s">
         <v>241</v>
       </c>
       <c r="E16" t="s">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="F16" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H16" t="s">
-        <v>303</v>
-      </c>
-      <c r="I16" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
       <c r="B17" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>356</v>
+        <v>408</v>
       </c>
       <c r="D17" t="s">
         <v>241</v>
       </c>
       <c r="E17" t="s">
-        <v>357</v>
+        <v>409</v>
       </c>
       <c r="F17" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H17" t="s">
-        <v>303</v>
-      </c>
-      <c r="I17" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>358</v>
+        <v>410</v>
       </c>
       <c r="D18" t="s">
         <v>241</v>
       </c>
       <c r="E18" t="s">
-        <v>359</v>
+        <v>411</v>
       </c>
       <c r="F18" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H18" t="s">
-        <v>303</v>
-      </c>
-      <c r="I18" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
       <c r="B19" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>360</v>
+        <v>412</v>
       </c>
       <c r="D19" t="s">
         <v>241</v>
       </c>
       <c r="E19" t="s">
-        <v>361</v>
+        <v>413</v>
       </c>
       <c r="F19" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>232</v>
+        <v>325</v>
       </c>
       <c r="H19" t="s">
-        <v>303</v>
-      </c>
-      <c r="I19" t="s">
-        <v>245</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C20" t="s">
+        <v>414</v>
+      </c>
+      <c r="D20" t="s">
+        <v>241</v>
+      </c>
+      <c r="E20" t="s">
+        <v>415</v>
+      </c>
+      <c r="F20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" t="s">
+        <v>325</v>
+      </c>
+      <c r="H20" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" t="s">
+        <v>416</v>
+      </c>
+      <c r="D21" t="s">
+        <v>241</v>
+      </c>
+      <c r="E21" t="s">
+        <v>417</v>
+      </c>
+      <c r="F21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" t="s">
+        <v>325</v>
+      </c>
+      <c r="H21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" t="s">
+        <v>418</v>
+      </c>
+      <c r="D22" t="s">
+        <v>241</v>
+      </c>
+      <c r="E22" t="s">
+        <v>419</v>
+      </c>
+      <c r="F22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" t="s">
+        <v>325</v>
+      </c>
+      <c r="H22" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" t="s">
+        <v>420</v>
+      </c>
+      <c r="D23" t="s">
+        <v>241</v>
+      </c>
+      <c r="E23" t="s">
+        <v>421</v>
+      </c>
+      <c r="F23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" t="s">
+        <v>325</v>
+      </c>
+      <c r="H23" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" t="s">
+        <v>422</v>
+      </c>
+      <c r="D24" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" t="s">
+        <v>423</v>
+      </c>
+      <c r="F24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" t="s">
+        <v>325</v>
+      </c>
+      <c r="H24" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" t="s">
+        <v>192</v>
+      </c>
+      <c r="C25" t="s">
+        <v>424</v>
+      </c>
+      <c r="D25" t="s">
+        <v>241</v>
+      </c>
+      <c r="E25" t="s">
+        <v>425</v>
+      </c>
+      <c r="F25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" t="s">
+        <v>325</v>
+      </c>
+      <c r="H25" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" t="s">
+        <v>192</v>
+      </c>
+      <c r="C26" t="s">
+        <v>426</v>
+      </c>
+      <c r="D26" t="s">
+        <v>241</v>
+      </c>
+      <c r="E26" t="s">
+        <v>427</v>
+      </c>
+      <c r="F26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" t="s">
+        <v>325</v>
+      </c>
+      <c r="H26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" t="s">
+        <v>192</v>
+      </c>
+      <c r="C27" t="s">
+        <v>428</v>
+      </c>
+      <c r="D27" t="s">
+        <v>241</v>
+      </c>
+      <c r="E27" t="s">
+        <v>429</v>
+      </c>
+      <c r="F27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" t="s">
+        <v>325</v>
+      </c>
+      <c r="H27" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" t="s">
+        <v>430</v>
+      </c>
+      <c r="D28" t="s">
+        <v>241</v>
+      </c>
+      <c r="E28" t="s">
+        <v>431</v>
+      </c>
+      <c r="F28" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" t="s">
+        <v>325</v>
+      </c>
+      <c r="H28" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" t="s">
+        <v>432</v>
+      </c>
+      <c r="D29" t="s">
+        <v>241</v>
+      </c>
+      <c r="E29" t="s">
+        <v>433</v>
+      </c>
+      <c r="F29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" t="s">
+        <v>325</v>
+      </c>
+      <c r="H29" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" t="s">
+        <v>434</v>
+      </c>
+      <c r="D30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E30" t="s">
+        <v>435</v>
+      </c>
+      <c r="F30" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" t="s">
+        <v>325</v>
+      </c>
+      <c r="H30" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" t="s">
+        <v>192</v>
+      </c>
+      <c r="C31" t="s">
+        <v>436</v>
+      </c>
+      <c r="D31" t="s">
+        <v>241</v>
+      </c>
+      <c r="E31" t="s">
+        <v>437</v>
+      </c>
+      <c r="F31" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" t="s">
+        <v>325</v>
+      </c>
+      <c r="H31" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C32" t="s">
+        <v>438</v>
+      </c>
+      <c r="D32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E32" t="s">
+        <v>439</v>
+      </c>
+      <c r="F32" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" t="s">
+        <v>325</v>
+      </c>
+      <c r="H32" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" t="s">
+        <v>192</v>
+      </c>
+      <c r="C33" t="s">
+        <v>440</v>
+      </c>
+      <c r="D33" t="s">
+        <v>241</v>
+      </c>
+      <c r="E33" t="s">
+        <v>441</v>
+      </c>
+      <c r="F33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" t="s">
+        <v>325</v>
+      </c>
+      <c r="H33" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" t="s">
+        <v>192</v>
+      </c>
+      <c r="C34" t="s">
+        <v>442</v>
+      </c>
+      <c r="D34" t="s">
+        <v>241</v>
+      </c>
+      <c r="E34" t="s">
+        <v>443</v>
+      </c>
+      <c r="F34" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" t="s">
+        <v>325</v>
+      </c>
+      <c r="H34" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" t="s">
+        <v>444</v>
+      </c>
+      <c r="D35" t="s">
+        <v>241</v>
+      </c>
+      <c r="E35" t="s">
+        <v>445</v>
+      </c>
+      <c r="F35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" t="s">
+        <v>325</v>
+      </c>
+      <c r="H35" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -3971,13 +4544,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53B1848-4D56-4187-89FF-9B80356B6D6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F0B0A1E-09F3-43F4-A4A9-84DC7AA3497A}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -4011,22 +4584,22 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>301</v>
+        <v>354</v>
       </c>
       <c r="D5" t="s">
         <v>241</v>
       </c>
       <c r="E5" t="s">
-        <v>302</v>
+        <v>355</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I5" t="s">
         <v>245</v>
@@ -4037,22 +4610,22 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>304</v>
+        <v>356</v>
       </c>
       <c r="D6" t="s">
         <v>241</v>
       </c>
       <c r="E6" t="s">
-        <v>305</v>
+        <v>357</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I6" t="s">
         <v>245</v>
@@ -4063,22 +4636,22 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>306</v>
+        <v>358</v>
       </c>
       <c r="D7" t="s">
         <v>241</v>
       </c>
       <c r="E7" t="s">
-        <v>307</v>
+        <v>359</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I7" t="s">
         <v>245</v>
@@ -4089,22 +4662,22 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="D8" t="s">
         <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>309</v>
+        <v>361</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I8" t="s">
         <v>245</v>
@@ -4115,22 +4688,22 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>310</v>
+        <v>362</v>
       </c>
       <c r="D9" t="s">
         <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>311</v>
+        <v>363</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I9" t="s">
         <v>245</v>
@@ -4141,22 +4714,22 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>312</v>
+        <v>364</v>
       </c>
       <c r="D10" t="s">
         <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H10" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I10" t="s">
         <v>245</v>
@@ -4167,22 +4740,22 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>314</v>
+        <v>366</v>
       </c>
       <c r="D11" t="s">
         <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>315</v>
+        <v>367</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H11" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I11" t="s">
         <v>245</v>
@@ -4193,22 +4766,22 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>316</v>
+        <v>368</v>
       </c>
       <c r="D12" t="s">
         <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>317</v>
+        <v>369</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H12" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I12" t="s">
         <v>245</v>
@@ -4219,22 +4792,22 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>318</v>
+        <v>370</v>
       </c>
       <c r="D13" t="s">
         <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I13" t="s">
         <v>245</v>
@@ -4245,22 +4818,22 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="D14" t="s">
         <v>241</v>
       </c>
       <c r="E14" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I14" t="s">
         <v>245</v>
@@ -4271,22 +4844,22 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="D15" t="s">
         <v>241</v>
       </c>
       <c r="E15" t="s">
-        <v>323</v>
+        <v>375</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H15" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I15" t="s">
         <v>245</v>
@@ -4297,22 +4870,22 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>324</v>
+        <v>376</v>
       </c>
       <c r="D16" t="s">
         <v>241</v>
       </c>
       <c r="E16" t="s">
+        <v>377</v>
+      </c>
+      <c r="F16" t="s">
+        <v>233</v>
+      </c>
+      <c r="G16" t="s">
+        <v>232</v>
+      </c>
+      <c r="H16" t="s">
         <v>325</v>
-      </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" t="s">
-        <v>303</v>
       </c>
       <c r="I16" t="s">
         <v>245</v>
@@ -4323,22 +4896,22 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>326</v>
+        <v>378</v>
       </c>
       <c r="D17" t="s">
         <v>241</v>
       </c>
       <c r="E17" t="s">
-        <v>327</v>
+        <v>379</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I17" t="s">
         <v>245</v>
@@ -4349,22 +4922,22 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>328</v>
+        <v>380</v>
       </c>
       <c r="D18" t="s">
         <v>241</v>
       </c>
       <c r="E18" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I18" t="s">
         <v>245</v>
@@ -4375,22 +4948,22 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="D19" t="s">
         <v>241</v>
       </c>
       <c r="E19" t="s">
-        <v>331</v>
+        <v>383</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="I19" t="s">
         <v>245</v>
@@ -4402,6 +4975,437 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9578D9AA-F5C0-4D68-82DA-ADF2C17A4B97}">
+  <dimension ref="B3:I19"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="3" spans="2:9">
+      <c r="B3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
+      <c r="B4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E5" t="s">
+        <v>324</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>325</v>
+      </c>
+      <c r="I5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>326</v>
+      </c>
+      <c r="D6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" t="s">
+        <v>327</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>325</v>
+      </c>
+      <c r="I6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" t="s">
+        <v>329</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>325</v>
+      </c>
+      <c r="I7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" t="s">
+        <v>331</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>325</v>
+      </c>
+      <c r="I8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>332</v>
+      </c>
+      <c r="D9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E9" t="s">
+        <v>333</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>325</v>
+      </c>
+      <c r="I9" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>334</v>
+      </c>
+      <c r="D10" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>325</v>
+      </c>
+      <c r="I10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E11" t="s">
+        <v>337</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>325</v>
+      </c>
+      <c r="I11" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D12" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>325</v>
+      </c>
+      <c r="I12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>340</v>
+      </c>
+      <c r="D13" t="s">
+        <v>241</v>
+      </c>
+      <c r="E13" t="s">
+        <v>341</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" t="s">
+        <v>325</v>
+      </c>
+      <c r="I13" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>342</v>
+      </c>
+      <c r="D14" t="s">
+        <v>241</v>
+      </c>
+      <c r="E14" t="s">
+        <v>343</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" t="s">
+        <v>325</v>
+      </c>
+      <c r="I14" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>344</v>
+      </c>
+      <c r="D15" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" t="s">
+        <v>345</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>325</v>
+      </c>
+      <c r="I15" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>346</v>
+      </c>
+      <c r="D16" t="s">
+        <v>241</v>
+      </c>
+      <c r="E16" t="s">
+        <v>347</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" t="s">
+        <v>325</v>
+      </c>
+      <c r="I16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>348</v>
+      </c>
+      <c r="D17" t="s">
+        <v>241</v>
+      </c>
+      <c r="E17" t="s">
+        <v>349</v>
+      </c>
+      <c r="F17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" t="s">
+        <v>325</v>
+      </c>
+      <c r="I17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>350</v>
+      </c>
+      <c r="D18" t="s">
+        <v>241</v>
+      </c>
+      <c r="E18" t="s">
+        <v>351</v>
+      </c>
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I18" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>352</v>
+      </c>
+      <c r="D19" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" t="s">
+        <v>353</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" t="s">
+        <v>325</v>
+      </c>
+      <c r="I19" t="s">
+        <v>245</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:S43"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -5413,14 +6417,150 @@
         <v>245</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="17.649999999999999" thickBot="1">
+    <row r="33" spans="2:19">
+      <c r="M33" t="s">
+        <v>17</v>
+      </c>
+      <c r="N33" t="s">
+        <v>300</v>
+      </c>
+      <c r="O33" t="s">
+        <v>241</v>
+      </c>
+      <c r="P33" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>25</v>
+      </c>
+      <c r="R33" t="s">
+        <v>35</v>
+      </c>
+      <c r="S33" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19">
+      <c r="M34" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" t="s">
+        <v>302</v>
+      </c>
+      <c r="O34" t="s">
+        <v>241</v>
+      </c>
+      <c r="P34" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>25</v>
+      </c>
+      <c r="R34" t="s">
+        <v>35</v>
+      </c>
+      <c r="S34" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19">
+      <c r="M35" t="s">
+        <v>17</v>
+      </c>
+      <c r="N35" t="s">
+        <v>304</v>
+      </c>
+      <c r="O35" t="s">
+        <v>241</v>
+      </c>
+      <c r="P35" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>25</v>
+      </c>
+      <c r="R35" t="s">
+        <v>35</v>
+      </c>
+      <c r="S35" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19">
+      <c r="M36" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" t="s">
+        <v>306</v>
+      </c>
+      <c r="O36" t="s">
+        <v>241</v>
+      </c>
+      <c r="P36" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>25</v>
+      </c>
+      <c r="R36" t="s">
+        <v>35</v>
+      </c>
+      <c r="S36" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19">
+      <c r="M37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" t="s">
+        <v>308</v>
+      </c>
+      <c r="O37" t="s">
+        <v>241</v>
+      </c>
+      <c r="P37" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>25</v>
+      </c>
+      <c r="R37" t="s">
+        <v>35</v>
+      </c>
+      <c r="S37" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" ht="17.649999999999999" thickBot="1">
       <c r="B38" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="2:7" ht="15" thickTop="1" thickBot="1">
+      <c r="M38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>310</v>
+      </c>
+      <c r="O38" t="s">
+        <v>241</v>
+      </c>
+      <c r="P38" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>25</v>
+      </c>
+      <c r="R38" t="s">
+        <v>35</v>
+      </c>
+      <c r="S38" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" ht="15" thickTop="1" thickBot="1">
       <c r="B39" s="5" t="s">
         <v>218</v>
       </c>
@@ -5439,8 +6579,29 @@
       <c r="G39" s="5" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="40" spans="2:7">
+      <c r="M39" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" t="s">
+        <v>312</v>
+      </c>
+      <c r="O39" t="s">
+        <v>241</v>
+      </c>
+      <c r="P39" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>25</v>
+      </c>
+      <c r="R39" t="s">
+        <v>35</v>
+      </c>
+      <c r="S39" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="2:19">
       <c r="B40" t="s">
         <v>17</v>
       </c>
@@ -5459,8 +6620,29 @@
       <c r="G40" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="41" spans="2:7">
+      <c r="M40" t="s">
+        <v>17</v>
+      </c>
+      <c r="N40" t="s">
+        <v>314</v>
+      </c>
+      <c r="O40" t="s">
+        <v>241</v>
+      </c>
+      <c r="P40" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>25</v>
+      </c>
+      <c r="R40" t="s">
+        <v>35</v>
+      </c>
+      <c r="S40" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="41" spans="2:19">
       <c r="C41" t="s">
         <v>223</v>
       </c>
@@ -5476,8 +6658,29 @@
       <c r="G41" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="42" spans="2:7">
+      <c r="M41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" t="s">
+        <v>316</v>
+      </c>
+      <c r="O41" t="s">
+        <v>241</v>
+      </c>
+      <c r="P41" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>25</v>
+      </c>
+      <c r="R41" t="s">
+        <v>35</v>
+      </c>
+      <c r="S41" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19">
       <c r="B42" t="s">
         <v>192</v>
       </c>
@@ -5493,8 +6696,29 @@
       <c r="F42" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="43" spans="2:7">
+      <c r="M42" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" t="s">
+        <v>318</v>
+      </c>
+      <c r="O42" t="s">
+        <v>241</v>
+      </c>
+      <c r="P42" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>25</v>
+      </c>
+      <c r="R42" t="s">
+        <v>35</v>
+      </c>
+      <c r="S42" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19">
       <c r="C43" t="s">
         <v>227</v>
       </c>
@@ -5506,6 +6730,27 @@
       </c>
       <c r="F43" t="s">
         <v>185</v>
+      </c>
+      <c r="M43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>320</v>
+      </c>
+      <c r="O43" t="s">
+        <v>241</v>
+      </c>
+      <c r="P43" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>25</v>
+      </c>
+      <c r="R43" t="s">
+        <v>35</v>
+      </c>
+      <c r="S43" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -5516,7 +6761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75"/>
@@ -5794,7 +7039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
@@ -6380,7 +7625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
@@ -8020,7 +9265,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>

--- a/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F3D4AD-90ED-4615-BCB1-90223D0F843E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD96C19-D80C-4096-B459-6EDAD61A9421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -775,7 +775,7 @@
     <t>elc_spv_HRV_001</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 1</t>
+    <t>solar electricity near Split (cluster 1)</t>
   </si>
   <si>
     <t>TWh</t>
@@ -784,229 +784,229 @@
     <t>elc_spv_HRV_002</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 2</t>
+    <t>solar electricity near Split (cluster 2)</t>
   </si>
   <si>
     <t>elc_spv_HRV_003</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 3</t>
+    <t>solar electricity near Rijeka (cluster 3)</t>
   </si>
   <si>
     <t>elc_spv_HRV_004</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 4</t>
+    <t>solar electricity near Rijeka (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_HRV_005</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 5</t>
+    <t>solar electricity near Rijeka (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_HRV_006</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 6</t>
+    <t>solar electricity near Zadar (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_HRV_007</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 7</t>
+    <t>solar electricity near Zadar (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_HRV_008</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 8</t>
+    <t>solar electricity near Zagreb (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_HRV_009</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 9</t>
+    <t>solar electricity near Varazdin (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_HRV_010</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 10</t>
+    <t>solar electricity near Zagreb (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_HRV_011</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 11</t>
+    <t>solar electricity near Osijek (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_HRV_012</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 12</t>
+    <t>solar electricity near Osijek (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_HRV_013</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 13</t>
+    <t>solar electricity near Osijek (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_HRV_014</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 14</t>
+    <t>solar electricity near Zagreb (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_HRV_015</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 15</t>
+    <t>solar electricity near Zagreb (cluster 15)</t>
   </si>
   <si>
     <t>elc_wof_HRV_001</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 1</t>
+    <t>wind offshore electricity near Pula (cluster 1)</t>
   </si>
   <si>
     <t>elc_wof_HRV_002</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 2</t>
+    <t>wind offshore electricity near Split (cluster 2)</t>
   </si>
   <si>
     <t>elc_wof_HRV_003</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 3</t>
+    <t>wind offshore electricity near Split (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_HRV_004</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 4</t>
+    <t>wind offshore electricity near Split (cluster 4)</t>
   </si>
   <si>
     <t>elc_wof_HRV_005</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 5</t>
+    <t>wind offshore electricity near Zadar (cluster 5)</t>
   </si>
   <si>
     <t>elc_wof_HRV_006</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 6</t>
+    <t>wind offshore electricity near Zadar (cluster 6)</t>
   </si>
   <si>
     <t>elc_wof_HRV_007</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 7</t>
+    <t>wind offshore electricity near Split (cluster 7)</t>
   </si>
   <si>
     <t>elc_wof_HRV_008</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 8</t>
+    <t>wind offshore electricity near Split (cluster 8)</t>
   </si>
   <si>
     <t>elc_wof_HRV_009</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 9</t>
+    <t>wind offshore electricity near Split (cluster 9)</t>
   </si>
   <si>
     <t>elc_wof_HRV_010</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 10</t>
+    <t>wind offshore electricity near Split (cluster 10)</t>
   </si>
   <si>
     <t>elc_wof_HRV_011</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 11</t>
+    <t>wind offshore electricity near Split (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_HRV_001</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 1</t>
+    <t>wind onshore electricity near Split (cluster 1)</t>
   </si>
   <si>
     <t>elc_won_HRV_002</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 2</t>
+    <t>wind onshore electricity near Split (cluster 2)</t>
   </si>
   <si>
     <t>elc_won_HRV_003</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 3</t>
+    <t>wind onshore electricity near Rijeka (cluster 3)</t>
   </si>
   <si>
     <t>elc_won_HRV_004</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 4</t>
+    <t>wind onshore electricity near Rijeka (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_HRV_005</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 5</t>
+    <t>wind onshore electricity near Split (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_HRV_006</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 6</t>
+    <t>wind onshore electricity near Zadar (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_HRV_007</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 7</t>
+    <t>wind onshore electricity near Zadar (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_HRV_008</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 8</t>
+    <t>wind onshore electricity near Osijek (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_HRV_009</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 9</t>
+    <t>wind onshore electricity near Osijek (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_HRV_010</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 10</t>
+    <t>wind onshore electricity near Zagreb (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_HRV_011</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 11</t>
+    <t>wind onshore electricity near Zagreb (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_HRV_012</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 12</t>
+    <t>wind onshore electricity near Varazdin (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_HRV_013</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 13</t>
+    <t>wind onshore electricity near Zagreb (cluster 13)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -3793,7 +3793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE3CBE1-B133-430B-AC96-CB0323706611}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95850B7F-B4B9-49B8-8CFB-138AD6371010}">
   <dimension ref="B3:H35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -4544,7 +4544,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F0B0A1E-09F3-43F4-A4A9-84DC7AA3497A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0F72C9-7715-4267-A0FD-9B8CB8BEC4FF}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -4975,7 +4975,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9578D9AA-F5C0-4D68-82DA-ADF2C17A4B97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC214772-788C-40D5-86B5-5D27D1990048}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
